--- a/Промежуточная таблица 3.xlsx
+++ b/Промежуточная таблица 3.xlsx
@@ -77,10 +77,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -3720,39 +3721,45 @@
           <t>ДО: ДО1</t>
         </is>
       </c>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -4162,21 +4169,21 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n">
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n">
         <v>4303</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="5" t="n">
         <v>1996</v>
       </c>
-      <c r="G16" s="4" t="n"/>
+      <c r="G16" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4184,39 +4191,45 @@
           <t>ДО: ДО2</t>
         </is>
       </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -4533,21 +4546,21 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n">
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n">
         <v>2493</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="5" t="n">
         <v>1021</v>
       </c>
-      <c r="G30" s="4" t="n"/>
+      <c r="G30" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -4555,39 +4568,45 @@
           <t>ДО: ДО3</t>
         </is>
       </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -4904,21 +4923,21 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n">
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n">
         <v>4521</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="5" t="n">
         <v>1296</v>
       </c>
-      <c r="G44" s="4" t="n"/>
+      <c r="G44" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4926,39 +4945,45 @@
           <t>ДО: ДО4</t>
         </is>
       </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -5275,21 +5300,21 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n">
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n">
         <v>2873</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="F58" s="5" t="n">
         <v>1215</v>
       </c>
-      <c r="G58" s="4" t="n"/>
+      <c r="G58" s="5" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5297,39 +5322,45 @@
           <t>ДО: ДО5</t>
         </is>
       </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -5646,21 +5677,21 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B72" s="4" t="n"/>
-      <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="n">
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n">
         <v>3147</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="F72" s="5" t="n">
         <v>971</v>
       </c>
-      <c r="G72" s="4" t="n"/>
+      <c r="G72" s="5" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5668,39 +5699,45 @@
           <t>ДО: ДО6</t>
         </is>
       </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -6017,21 +6054,21 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B86" s="4" t="n"/>
-      <c r="C86" s="4" t="n"/>
-      <c r="D86" s="4" t="n"/>
-      <c r="E86" s="4" t="n">
+      <c r="B86" s="5" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="5" t="n">
         <v>2973</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="5" t="n">
         <v>1589</v>
       </c>
-      <c r="G86" s="4" t="n"/>
+      <c r="G86" s="5" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6039,39 +6076,45 @@
           <t>ДО: ДО7</t>
         </is>
       </c>
+      <c r="B88" s="3" t="n"/>
+      <c r="C88" s="3" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -6388,21 +6431,21 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B100" s="4" t="n"/>
-      <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="4" t="n">
+      <c r="B100" s="5" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="5" t="n">
         <v>3342</v>
       </c>
-      <c r="F100" s="4" t="n">
+      <c r="F100" s="5" t="n">
         <v>1728</v>
       </c>
-      <c r="G100" s="4" t="n"/>
+      <c r="G100" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6410,39 +6453,45 @@
           <t>ДО: ДО8</t>
         </is>
       </c>
+      <c r="B102" s="3" t="n"/>
+      <c r="C102" s="3" t="n"/>
+      <c r="D102" s="3" t="n"/>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="3" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G103" s="3" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -6759,21 +6808,21 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B114" s="4" t="n"/>
-      <c r="C114" s="4" t="n"/>
-      <c r="D114" s="4" t="n"/>
-      <c r="E114" s="4" t="n">
+      <c r="B114" s="5" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="5" t="n">
         <v>4073</v>
       </c>
-      <c r="F114" s="4" t="n">
+      <c r="F114" s="5" t="n">
         <v>798</v>
       </c>
-      <c r="G114" s="4" t="n"/>
+      <c r="G114" s="5" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6781,39 +6830,45 @@
           <t>ДО: ДО9</t>
         </is>
       </c>
+      <c r="B116" s="3" t="n"/>
+      <c r="C116" s="3" t="n"/>
+      <c r="D116" s="3" t="n"/>
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="3" t="n"/>
+      <c r="G116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="F117" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G117" s="3" t="inlineStr">
+      <c r="G117" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -7130,21 +7185,21 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B128" s="4" t="n"/>
-      <c r="C128" s="4" t="n"/>
-      <c r="D128" s="4" t="n"/>
-      <c r="E128" s="4" t="n">
+      <c r="B128" s="5" t="n"/>
+      <c r="C128" s="5" t="n"/>
+      <c r="D128" s="5" t="n"/>
+      <c r="E128" s="5" t="n">
         <v>3936</v>
       </c>
-      <c r="F128" s="4" t="n">
+      <c r="F128" s="5" t="n">
         <v>1248</v>
       </c>
-      <c r="G128" s="4" t="n"/>
+      <c r="G128" s="5" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7152,39 +7207,45 @@
           <t>ДО: ДО10</t>
         </is>
       </c>
+      <c r="B130" s="3" t="n"/>
+      <c r="C130" s="3" t="n"/>
+      <c r="D130" s="3" t="n"/>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E131" s="3" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ (контрагент должен ДО)</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr">
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ (ДО должно контрагенту)</t>
         </is>
       </c>
-      <c r="G131" s="3" t="inlineStr">
+      <c r="G131" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен</t>
         </is>
@@ -7501,35 +7562,23 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="4" t="inlineStr">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B142" s="4" t="n"/>
-      <c r="C142" s="4" t="n"/>
-      <c r="D142" s="4" t="n"/>
-      <c r="E142" s="4" t="n">
+      <c r="B142" s="5" t="n"/>
+      <c r="C142" s="5" t="n"/>
+      <c r="D142" s="5" t="n"/>
+      <c r="E142" s="5" t="n">
         <v>3655</v>
       </c>
-      <c r="F142" s="4" t="n">
+      <c r="F142" s="5" t="n">
         <v>1086</v>
       </c>
-      <c r="G142" s="4" t="n"/>
+      <c r="G142" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A102:G102"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A88:G88"/>
-    <mergeCell ref="A116:G116"/>
-    <mergeCell ref="A130:G130"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A46:G46"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7542,51 +7591,68 @@
   </sheetPr>
   <dimension ref="A1:H142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 1</t>
         </is>
       </c>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ</t>
         </is>
@@ -7945,68 +8011,78 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="n">
         <v>4571</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="5" t="n">
         <v>1354</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="5" t="n">
         <v>4571</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="5" t="n">
         <v>1354</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 2</t>
         </is>
       </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ</t>
         </is>
@@ -8365,68 +8441,78 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="n">
         <v>4180</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="5" t="n">
         <v>1647</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" s="5" t="n">
         <v>4180</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="5" t="n">
         <v>1647</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 3</t>
         </is>
       </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ</t>
         </is>
@@ -8785,68 +8871,78 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="B44" s="5" t="inlineStr"/>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="n">
         <v>3608</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="5" t="n">
         <v>695</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="5" t="n">
         <v>3608</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="5" t="n">
         <v>695</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 4</t>
         </is>
       </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ</t>
         </is>
@@ -9173,68 +9269,78 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="E58" t="n">
+      <c r="B58" s="5" t="inlineStr"/>
+      <c r="C58" s="5" t="inlineStr"/>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
         <v>3026</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="5" t="n">
         <v>1271</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" s="5" t="n">
         <v>3026</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="5" t="n">
         <v>1271</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 5</t>
         </is>
       </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ</t>
         </is>
@@ -9561,68 +9667,78 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="E72" t="n">
+      <c r="B72" s="5" t="inlineStr"/>
+      <c r="C72" s="5" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
         <v>3482</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="5" t="n">
         <v>1209</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" s="5" t="n">
         <v>3482</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" s="5" t="n">
         <v>1209</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 6</t>
         </is>
       </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ</t>
         </is>
@@ -9949,68 +10065,78 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="E86" t="n">
+      <c r="B86" s="5" t="inlineStr"/>
+      <c r="C86" s="5" t="inlineStr"/>
+      <c r="D86" s="5" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
         <v>4134</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86" s="5" t="n">
         <v>575</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86" s="5" t="n">
         <v>4134</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H86" s="5" t="n">
         <v>575</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 7</t>
         </is>
       </c>
+      <c r="B88" s="3" t="n"/>
+      <c r="C88" s="3" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ</t>
         </is>
@@ -10337,68 +10463,78 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="E100" t="n">
+      <c r="B100" s="5" t="inlineStr"/>
+      <c r="C100" s="5" t="inlineStr"/>
+      <c r="D100" s="5" t="inlineStr"/>
+      <c r="E100" s="5" t="n">
         <v>2226</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100" s="5" t="n">
         <v>1561</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G100" s="5" t="n">
         <v>2226</v>
       </c>
-      <c r="H100" t="n">
+      <c r="H100" s="5" t="n">
         <v>1561</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 8</t>
         </is>
       </c>
+      <c r="B102" s="3" t="n"/>
+      <c r="C102" s="3" t="n"/>
+      <c r="D102" s="3" t="n"/>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="3" t="n"/>
+      <c r="H102" s="3" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H103" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ</t>
         </is>
@@ -10725,68 +10861,78 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="E114" t="n">
+      <c r="B114" s="5" t="inlineStr"/>
+      <c r="C114" s="5" t="inlineStr"/>
+      <c r="D114" s="5" t="inlineStr"/>
+      <c r="E114" s="5" t="n">
         <v>2958</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114" s="5" t="n">
         <v>1658</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G114" s="5" t="n">
         <v>2958</v>
       </c>
-      <c r="H114" t="n">
+      <c r="H114" s="5" t="n">
         <v>1658</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 9</t>
         </is>
       </c>
+      <c r="B116" s="3" t="n"/>
+      <c r="C116" s="3" t="n"/>
+      <c r="D116" s="3" t="n"/>
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="3" t="n"/>
+      <c r="G116" s="3" t="n"/>
+      <c r="H116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G117" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H117" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ</t>
         </is>
@@ -11113,68 +11259,78 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="E128" t="n">
+      <c r="B128" s="5" t="inlineStr"/>
+      <c r="C128" s="5" t="inlineStr"/>
+      <c r="D128" s="5" t="inlineStr"/>
+      <c r="E128" s="5" t="n">
         <v>3825</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128" s="5" t="n">
         <v>1848</v>
       </c>
-      <c r="G128" t="n">
+      <c r="G128" s="5" t="n">
         <v>3825</v>
       </c>
-      <c r="H128" t="n">
+      <c r="H128" s="5" t="n">
         <v>1848</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 10</t>
         </is>
       </c>
+      <c r="B130" s="3" t="n"/>
+      <c r="C130" s="3" t="n"/>
+      <c r="D130" s="3" t="n"/>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="3" t="n"/>
+      <c r="H130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G131" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H131" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ</t>
         </is>
@@ -11501,21 +11657,24 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="E142" t="n">
+      <c r="B142" s="5" t="inlineStr"/>
+      <c r="C142" s="5" t="inlineStr"/>
+      <c r="D142" s="5" t="inlineStr"/>
+      <c r="E142" s="5" t="n">
         <v>3306</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F142" s="5" t="n">
         <v>1130</v>
       </c>
-      <c r="G142" t="n">
+      <c r="G142" s="5" t="n">
         <v>3306</v>
       </c>
-      <c r="H142" t="n">
+      <c r="H142" s="5" t="n">
         <v>1130</v>
       </c>
     </row>
@@ -11534,7 +11693,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
@@ -11598,7 +11757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -11701,7 +11860,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -11804,7 +11963,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -11907,7 +12066,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -12010,7 +12169,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -12113,7 +12272,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -12216,7 +12375,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12319,7 +12478,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -12422,7 +12581,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -12525,7 +12684,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -12628,7 +12787,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -12731,7 +12890,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -12834,7 +12993,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -12937,7 +13096,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -13040,7 +13199,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -13143,7 +13302,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -13246,7 +13405,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -13349,7 +13508,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -13452,7 +13611,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -13555,7 +13714,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -13658,7 +13817,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -13761,7 +13920,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -13864,7 +14023,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -13967,7 +14126,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -14070,7 +14229,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -14173,7 +14332,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -14276,7 +14435,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -14379,7 +14538,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -14482,7 +14641,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -14585,7 +14744,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -14688,7 +14847,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -14791,7 +14950,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -14894,7 +15053,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -14997,7 +15156,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -15100,7 +15259,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -15203,7 +15362,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -15306,7 +15465,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -15409,7 +15568,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -15512,7 +15671,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -15615,7 +15774,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -15718,7 +15877,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -15821,7 +15980,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -15924,7 +16083,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -16027,7 +16186,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -16130,7 +16289,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -16233,7 +16392,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -16336,7 +16495,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -16439,7 +16598,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -16542,7 +16701,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -16645,7 +16804,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -16748,7 +16907,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -16851,7 +17010,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -16954,7 +17113,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -17057,7 +17216,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -17160,7 +17319,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -17263,7 +17422,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -17366,7 +17525,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -17469,7 +17628,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ЗАЧЁТ</t>
+          <t>ОПЕРАЦИЯ ВЗАИМОЗАЧЁТА</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -20875,54 +21034,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ДО: ДО1</t>
         </is>
       </c>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен после зачёта</t>
         </is>
@@ -21410,78 +21577,86 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="n">
         <v>4303</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="5" t="n">
         <v>1996</v>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr"/>
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>ДО: ДО2</t>
         </is>
       </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен после зачёта</t>
         </is>
@@ -21858,78 +22033,86 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="n">
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="n">
         <v>2493</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" s="5" t="n">
         <v>1021</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr"/>
     </row>
     <row r="31"/>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>ДО: ДО3</t>
         </is>
       </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен после зачёта</t>
         </is>
@@ -22306,78 +22489,86 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="n">
+      <c r="B44" s="5" t="inlineStr"/>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="n">
         <v>4521</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="5" t="n">
         <v>1296</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="5" t="n">
         <v>1549</v>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="inlineStr"/>
     </row>
     <row r="45"/>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>ДО: ДО4</t>
         </is>
       </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен после зачёта</t>
         </is>
@@ -22754,78 +22945,86 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="n">
+      <c r="B58" s="5" t="inlineStr"/>
+      <c r="C58" s="5" t="inlineStr"/>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
         <v>2873</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="5" t="n">
         <v>1215</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" s="5" t="n">
         <v>1381</v>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="H58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="5" t="inlineStr"/>
     </row>
     <row r="59"/>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>ДО: ДО5</t>
         </is>
       </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+      <c r="I60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен после зачёта</t>
         </is>
@@ -23202,78 +23401,86 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="n">
+      <c r="B72" s="5" t="inlineStr"/>
+      <c r="C72" s="5" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
         <v>3147</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="5" t="n">
         <v>971</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" s="5" t="n">
         <v>2136</v>
       </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="H72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="5" t="inlineStr"/>
     </row>
     <row r="73"/>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>ДО: ДО6</t>
         </is>
       </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен после зачёта</t>
         </is>
@@ -23650,78 +23857,86 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="n">
+      <c r="B86" s="5" t="inlineStr"/>
+      <c r="C86" s="5" t="inlineStr"/>
+      <c r="D86" s="5" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
         <v>2973</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86" s="5" t="n">
         <v>1589</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86" s="5" t="n">
         <v>2211</v>
       </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="H86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="5" t="inlineStr"/>
     </row>
     <row r="87"/>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>ДО: ДО7</t>
         </is>
       </c>
+      <c r="B88" s="3" t="n"/>
+      <c r="C88" s="3" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
+      <c r="I88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I89" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен после зачёта</t>
         </is>
@@ -24098,78 +24313,86 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="n">
+      <c r="B100" s="5" t="inlineStr"/>
+      <c r="C100" s="5" t="inlineStr"/>
+      <c r="D100" s="5" t="inlineStr"/>
+      <c r="E100" s="5" t="n">
         <v>3342</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100" s="5" t="n">
         <v>1728</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G100" s="5" t="n">
         <v>3270</v>
       </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="H100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="5" t="inlineStr"/>
     </row>
     <row r="101"/>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>ДО: ДО8</t>
         </is>
       </c>
+      <c r="B102" s="3" t="n"/>
+      <c r="C102" s="3" t="n"/>
+      <c r="D102" s="3" t="n"/>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="3" t="n"/>
+      <c r="H102" s="3" t="n"/>
+      <c r="I102" s="3" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H103" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I103" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен после зачёта</t>
         </is>
@@ -24546,78 +24769,86 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="n">
+      <c r="B114" s="5" t="inlineStr"/>
+      <c r="C114" s="5" t="inlineStr"/>
+      <c r="D114" s="5" t="inlineStr"/>
+      <c r="E114" s="5" t="n">
         <v>4073</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114" s="5" t="n">
         <v>798</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G114" s="5" t="n">
         <v>3926</v>
       </c>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="H114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="5" t="inlineStr"/>
     </row>
     <row r="115"/>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>ДО: ДО9</t>
         </is>
       </c>
+      <c r="B116" s="3" t="n"/>
+      <c r="C116" s="3" t="n"/>
+      <c r="D116" s="3" t="n"/>
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="3" t="n"/>
+      <c r="G116" s="3" t="n"/>
+      <c r="H116" s="3" t="n"/>
+      <c r="I116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G117" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H117" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I117" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен после зачёта</t>
         </is>
@@ -24994,78 +25225,86 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="n">
+      <c r="B128" s="5" t="inlineStr"/>
+      <c r="C128" s="5" t="inlineStr"/>
+      <c r="D128" s="5" t="inlineStr"/>
+      <c r="E128" s="5" t="n">
         <v>3936</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128" s="5" t="n">
         <v>1248</v>
       </c>
-      <c r="G128" t="n">
+      <c r="G128" s="5" t="n">
         <v>3936</v>
       </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="inlineStr"/>
+      <c r="H128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="5" t="inlineStr"/>
     </row>
     <row r="129"/>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>ДО: ДО10</t>
         </is>
       </c>
+      <c r="B130" s="3" t="n"/>
+      <c r="C130" s="3" t="n"/>
+      <c r="D130" s="3" t="n"/>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="3" t="n"/>
+      <c r="H130" s="3" t="n"/>
+      <c r="I130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>Контрагент</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G131" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H131" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="I131" s="4" t="inlineStr">
         <is>
           <t>Кто кому должен после зачёта</t>
         </is>
@@ -25442,27 +25681,27 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>Итого по ДО</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="n">
+      <c r="B142" s="5" t="inlineStr"/>
+      <c r="C142" s="5" t="inlineStr"/>
+      <c r="D142" s="5" t="inlineStr"/>
+      <c r="E142" s="5" t="n">
         <v>3655</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F142" s="5" t="n">
         <v>1086</v>
       </c>
-      <c r="G142" t="n">
+      <c r="G142" s="5" t="n">
         <v>3655</v>
       </c>
-      <c r="H142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" t="inlineStr"/>
+      <c r="H142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="5" t="inlineStr"/>
     </row>
     <row r="143"/>
   </sheetData>
@@ -25490,49 +25729,56 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 1</t>
         </is>
       </c>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
@@ -25891,72 +26137,79 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="n">
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="n">
         <v>4571</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="5" t="n">
         <v>1354</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="5" t="n">
         <v>3217</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15"/>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 2</t>
         </is>
       </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
@@ -26315,72 +26568,79 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="n">
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="n">
         <v>4180</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" s="5" t="n">
         <v>1647</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29" s="5" t="n">
         <v>2533</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30"/>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 3</t>
         </is>
       </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
@@ -26739,72 +26999,79 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="n">
+      <c r="B44" s="5" t="inlineStr"/>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="n">
         <v>3608</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="5" t="n">
         <v>695</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="5" t="n">
         <v>2913</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45"/>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 4</t>
         </is>
       </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
@@ -27131,72 +27398,79 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="n">
+      <c r="B58" s="5" t="inlineStr"/>
+      <c r="C58" s="5" t="inlineStr"/>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
         <v>3026</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58" s="5" t="n">
         <v>1271</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" s="5" t="n">
         <v>1755</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59"/>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 5</t>
         </is>
       </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n"/>
+      <c r="D60" s="3" t="n"/>
+      <c r="E60" s="3" t="n"/>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
@@ -27523,72 +27797,79 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="n">
+      <c r="B72" s="5" t="inlineStr"/>
+      <c r="C72" s="5" t="inlineStr"/>
+      <c r="D72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
         <v>3482</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="5" t="n">
         <v>1209</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" s="5" t="n">
         <v>2273</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73"/>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 6</t>
         </is>
       </c>
+      <c r="B74" s="3" t="n"/>
+      <c r="C74" s="3" t="n"/>
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
@@ -27915,72 +28196,79 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="n">
+      <c r="B86" s="5" t="inlineStr"/>
+      <c r="C86" s="5" t="inlineStr"/>
+      <c r="D86" s="5" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
         <v>4134</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86" s="5" t="n">
         <v>575</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86" s="5" t="n">
         <v>3559</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H86" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="87"/>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 7</t>
         </is>
       </c>
+      <c r="B88" s="3" t="n"/>
+      <c r="C88" s="3" t="n"/>
+      <c r="D88" s="3" t="n"/>
+      <c r="E88" s="3" t="n"/>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="3" t="n"/>
+      <c r="H88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
@@ -28307,72 +28595,79 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="n">
+      <c r="B100" s="5" t="inlineStr"/>
+      <c r="C100" s="5" t="inlineStr"/>
+      <c r="D100" s="5" t="inlineStr"/>
+      <c r="E100" s="5" t="n">
         <v>2226</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100" s="5" t="n">
         <v>1561</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G100" s="5" t="n">
         <v>665</v>
       </c>
-      <c r="H100" t="n">
+      <c r="H100" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101"/>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 8</t>
         </is>
       </c>
+      <c r="B102" s="3" t="n"/>
+      <c r="C102" s="3" t="n"/>
+      <c r="D102" s="3" t="n"/>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="3" t="n"/>
+      <c r="H102" s="3" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H103" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
@@ -28699,72 +28994,79 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="n">
+      <c r="B114" s="5" t="inlineStr"/>
+      <c r="C114" s="5" t="inlineStr"/>
+      <c r="D114" s="5" t="inlineStr"/>
+      <c r="E114" s="5" t="n">
         <v>2958</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114" s="5" t="n">
         <v>1658</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G114" s="5" t="n">
         <v>1300</v>
       </c>
-      <c r="H114" t="n">
+      <c r="H114" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="115"/>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 9</t>
         </is>
       </c>
+      <c r="B116" s="3" t="n"/>
+      <c r="C116" s="3" t="n"/>
+      <c r="D116" s="3" t="n"/>
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="3" t="n"/>
+      <c r="G116" s="3" t="n"/>
+      <c r="H116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G117" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H117" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
@@ -29091,72 +29393,79 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="n">
+      <c r="B128" s="5" t="inlineStr"/>
+      <c r="C128" s="5" t="inlineStr"/>
+      <c r="D128" s="5" t="inlineStr"/>
+      <c r="E128" s="5" t="n">
         <v>3825</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128" s="5" t="n">
         <v>1848</v>
       </c>
-      <c r="G128" t="n">
+      <c r="G128" s="5" t="n">
         <v>1977</v>
       </c>
-      <c r="H128" t="n">
+      <c r="H128" s="5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="129"/>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Контрагент: К/а 10</t>
         </is>
       </c>
+      <c r="B130" s="3" t="n"/>
+      <c r="C130" s="3" t="n"/>
+      <c r="D130" s="3" t="n"/>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="3" t="n"/>
+      <c r="H130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>ДО</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>Договор</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>Вид ДЗ</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>Сумма ДЗ до зачёта</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>Сумма КЗ до зачёта</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G131" s="4" t="inlineStr">
         <is>
           <t>Остаток ДЗ после зачёта</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H131" s="4" t="inlineStr">
         <is>
           <t>Остаток КЗ после зачёта</t>
         </is>
@@ -29483,24 +29792,24 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>Итого</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="n">
+      <c r="B142" s="5" t="inlineStr"/>
+      <c r="C142" s="5" t="inlineStr"/>
+      <c r="D142" s="5" t="inlineStr"/>
+      <c r="E142" s="5" t="n">
         <v>3306</v>
       </c>
-      <c r="F142" t="n">
+      <c r="F142" s="5" t="n">
         <v>1130</v>
       </c>
-      <c r="G142" t="n">
+      <c r="G142" s="5" t="n">
         <v>2176</v>
       </c>
-      <c r="H142" t="n">
+      <c r="H142" s="5" t="n">
         <v>0</v>
       </c>
     </row>
